--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187545</v>
+        <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>98748</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771407</v>
+        <v>771403</v>
       </c>
       <c r="R2" t="n">
-        <v>7215712</v>
+        <v>7215653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187551</v>
+        <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>98750</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771403</v>
+        <v>771407</v>
       </c>
       <c r="R3" t="n">
-        <v>7215653</v>
+        <v>7215712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187551</v>
+        <v>130187545</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>98837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771403</v>
+        <v>771407</v>
       </c>
       <c r="R2" t="n">
-        <v>7215653</v>
+        <v>7215712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187545</v>
+        <v>130187551</v>
       </c>
       <c r="B3" t="n">
-        <v>98837</v>
+        <v>80314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771407</v>
+        <v>771403</v>
       </c>
       <c r="R3" t="n">
-        <v>7215712</v>
+        <v>7215653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187545</v>
+        <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>98837</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771407</v>
+        <v>771403</v>
       </c>
       <c r="R2" t="n">
-        <v>7215712</v>
+        <v>7215653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187551</v>
+        <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>98837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771403</v>
+        <v>771407</v>
       </c>
       <c r="R3" t="n">
-        <v>7215653</v>
+        <v>7215712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>98837</v>
+        <v>98840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>80317</v>
+        <v>80343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>98840</v>
+        <v>98866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187551</v>
+        <v>130187545</v>
       </c>
       <c r="B2" t="n">
-        <v>80343</v>
+        <v>98867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771403</v>
+        <v>771407</v>
       </c>
       <c r="R2" t="n">
-        <v>7215653</v>
+        <v>7215712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187545</v>
+        <v>130187551</v>
       </c>
       <c r="B3" t="n">
-        <v>98866</v>
+        <v>80343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771407</v>
+        <v>771403</v>
       </c>
       <c r="R3" t="n">
-        <v>7215712</v>
+        <v>7215653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187545</v>
+        <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>98867</v>
+        <v>80343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771407</v>
+        <v>771403</v>
       </c>
       <c r="R2" t="n">
-        <v>7215712</v>
+        <v>7215653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187551</v>
+        <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>80343</v>
+        <v>98868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771403</v>
+        <v>771407</v>
       </c>
       <c r="R3" t="n">
-        <v>7215653</v>
+        <v>7215712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187551</v>
       </c>
       <c r="B2" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>98868</v>
+        <v>98870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38458-2025 artfynd.xlsx
+++ b/artfynd/A 38458-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130187545</v>
       </c>
       <c r="B3" t="n">
-        <v>98870</v>
+        <v>98874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
